--- a/artfynd/A 32065-2022 artfynd.xlsx
+++ b/artfynd/A 32065-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32065-2022 artfynd.xlsx
+++ b/artfynd/A 32065-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104305655</v>
+        <v>104305653</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412256.8437509324</v>
+        <v>412512</v>
       </c>
       <c r="R2" t="n">
-        <v>7068566.273625886</v>
+        <v>7068110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,24 +743,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104305659</v>
+        <v>119506210</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grimsåvallen, Jmt</t>
+          <t>Skog väster om Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412407.1035160191</v>
+        <v>412016</v>
       </c>
       <c r="R3" t="n">
-        <v>7068304.149695416</v>
+        <v>7068623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,62 +857,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104305657</v>
+        <v>119506191</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grimsåvallen, Jmt</t>
+          <t>Skog väster om Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412406.2761418242</v>
+        <v>412013</v>
       </c>
       <c r="R4" t="n">
-        <v>7068354.256754222</v>
+        <v>7068642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +938,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +963,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104305653</v>
+        <v>119506195</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grimsåvallen, Jmt</t>
+          <t>Skog väster om Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412511.333037174</v>
+        <v>412039</v>
       </c>
       <c r="R5" t="n">
-        <v>7068109.777657</v>
+        <v>7068682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,22 +1044,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,70 +1069,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104305654</v>
+        <v>104305658</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412260.8961139736</v>
+        <v>412416</v>
       </c>
       <c r="R6" t="n">
-        <v>7068552.421954254</v>
+        <v>7068301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,24 +1153,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,15 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104305661</v>
+        <v>119506193</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,34 +1193,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grimsåvallen, Jmt</t>
+          <t>Skog väster om Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412475.8083085269</v>
+        <v>412039</v>
       </c>
       <c r="R7" t="n">
-        <v>7068237.087521197</v>
+        <v>7068682</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,22 +1247,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,49 +1272,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104305660</v>
+        <v>104305657</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412462.5153207604</v>
+        <v>412406</v>
       </c>
       <c r="R8" t="n">
-        <v>7068253.85606698</v>
+        <v>7068354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,19 +1356,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104305658</v>
+        <v>119506192</v>
       </c>
       <c r="B9" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,34 +1396,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6443</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grimsåvallen, Jmt</t>
+          <t>Skog väster om Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>412415.8744928187</v>
+        <v>412039</v>
       </c>
       <c r="R9" t="n">
-        <v>7068300.360303059</v>
+        <v>7068682</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1450,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,27 +1475,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104305656</v>
+        <v>104305654</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>412330.4186213613</v>
+        <v>412261</v>
       </c>
       <c r="R10" t="n">
-        <v>7068419.300991734</v>
+        <v>7068552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,19 +1567,9 @@
           <t>2022-10-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1722,15 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506191</v>
+        <v>104305655</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,34 +1612,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog väster om Grimsåvallen, Jmt</t>
+          <t>Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412013</v>
+        <v>412257</v>
       </c>
       <c r="R11" t="n">
-        <v>7068642</v>
+        <v>7068566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,17 +1674,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,31 +1699,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506210</v>
+        <v>104305656</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,34 +1722,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog väster om Grimsåvallen, Jmt</t>
+          <t>Grimsåvallen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>412016</v>
+        <v>412331</v>
       </c>
       <c r="R12" t="n">
-        <v>7068623</v>
+        <v>7068419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,12 +1784,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,19 +1809,15 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32065-2022 artfynd.xlsx
+++ b/artfynd/A 32065-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119506210</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119506191</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119506195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119506193</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305657</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119506192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305654</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,8 +1873,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>